--- a/static/template.xlsx
+++ b/static/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr codeName="חוברת_עבודה_זו" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dan/Documents/projects/yanshuf/static/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dan/Documents/Workflow Sandbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF81E3A4-C604-5446-9EDE-9856E9EEEEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D11D50-9AE6-D049-B88F-49F392CD8CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="17380" tabRatio="825" xr2:uid="{14744205-2130-4719-A7F8-8F89D06F2CF6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17380" tabRatio="825" xr2:uid="{14744205-2130-4719-A7F8-8F89D06F2CF6}"/>
   </bookViews>
   <sheets>
     <sheet name="פרוטוקול בדיקה תקופתית" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">' ערכי DC'!$A$1:$H$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">טבלה24[#All]</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'ערכי AC'!$A$1:$D$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'פרוטוקול בדיקה תקופתית'!$A$1:$D$84</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'ריכוז ליקויים'!$A$1:$D$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">' ערכי DC'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'ערכי AC'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'פרוטוקול בדיקה תקופתית'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'ריכוז ליקויים'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="186">
   <si>
     <t>תיאור הבדיקה</t>
   </si>
@@ -758,6 +760,30 @@
   </si>
   <si>
     <t>מהפך 1</t>
+  </si>
+  <si>
+    <t>מהפך 2</t>
+  </si>
+  <si>
+    <t>מהפך 4</t>
+  </si>
+  <si>
+    <t>מהפך 5</t>
+  </si>
+  <si>
+    <t>מהפך 3</t>
+  </si>
+  <si>
+    <t>מהפך 6</t>
+  </si>
+  <si>
+    <t>מהפך 7</t>
+  </si>
+  <si>
+    <t>מהפך 8</t>
+  </si>
+  <si>
+    <t>מהפך 9</t>
   </si>
 </sst>
 </file>
@@ -850,7 +876,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="312">
     <border>
       <left/>
       <right/>
@@ -874,13 +900,89 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top/>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </bottom>
@@ -893,33 +995,18 @@
       <right style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <top style="thin">
         <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -929,32 +1016,3632 @@
         <color theme="4" tint="0.39997558519241921"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top/>
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -962,7 +4649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="338">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1000,40 +4687,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1046,50 +4712,953 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="108" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="110" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="112" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="116" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="118" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="120" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="121" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="122" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="124" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="126" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="128" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="132" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="134" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="136" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="138" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="140" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="142" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="143" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="144" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="146" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="147" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="148" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="150" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="151" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="152" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="154" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="156" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="158" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="161" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="169" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="170" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="171" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="174" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="175" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="176" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="177" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="179" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="180" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="181" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="183" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="185" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="187" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="188" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="192" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="193" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="194" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="196" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="207" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="208" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="209" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="212" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="213" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="214" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="215" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="216" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="217" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="221" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="222" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="223" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="224" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="225" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="226" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="227" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="231" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="232" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="233" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="234" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="235" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="237" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="238" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="239" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="240" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="241" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="242" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="244" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="245" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="246" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="247" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="248" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="249" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="250" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="251" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="252" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="253" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="254" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="255" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="256" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="257" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="258" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="259" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="260" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="261" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="262" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="263" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="264" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="265" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="266" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="267" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="268" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="269" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="270" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="271" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="272" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="273" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="274" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="275" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="276" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="277" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="278" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="279" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="280" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="281" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="282" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="283" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="284" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="285" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="286" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="287" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="288" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="289" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="290" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="291" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="292" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="293" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="294" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="295" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="296" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="297" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="298" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="299" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="300" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="301" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="302" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="303" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="304" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="305" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="306" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="307" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="308" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="309" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="310" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="311" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1832,7 +6401,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5408A944-6EDF-433C-86A5-9FC40FC04D8F}" name="טבלה24" displayName="טבלה24" ref="A1:D34" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5408A944-6EDF-433C-86A5-9FC40FC04D8F}" name="טבלה24" displayName="טבלה24" ref="A1:D42" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{61289872-4438-497E-8595-6E87059FC03D}" name="סעיף" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{C6D15FFB-BCE2-45F7-82D3-F4A1882BDBDB}" name="תיאור הבדיקה" dataDxfId="8"/>
@@ -2162,8 +6731,8 @@
   <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.1640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="43.33203125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" style="13" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="7" customWidth="1"/>
     <col min="4" max="4" width="28.83203125" style="7" customWidth="1"/>
     <col min="5" max="16384" width="8.83203125" style="7"/>
@@ -2187,24 +6756,24 @@
       <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="31"/>
+      <c r="D2" s="23"/>
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="30"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="30"/>
+      <c r="D3" s="22"/>
     </row>
     <row r="4" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="14" t="s">
         <v>62</v>
       </c>
       <c r="B4" s="3"/>
@@ -2212,135 +6781,135 @@
       <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="32"/>
+      <c r="C5" s="24"/>
     </row>
     <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="32"/>
+      <c r="C6" s="24"/>
     </row>
     <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="24"/>
     </row>
     <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="32"/>
+      <c r="C8" s="24"/>
     </row>
     <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
     </row>
     <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="32"/>
+      <c r="C11" s="24"/>
     </row>
     <row r="12" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="32"/>
+      <c r="C12" s="24"/>
     </row>
     <row r="13" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="61" t="s">
         <v>141</v>
       </c>
-      <c r="C13" s="32"/>
+      <c r="C13" s="24"/>
     </row>
     <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="32"/>
+      <c r="C14" s="24"/>
     </row>
     <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="32"/>
+      <c r="C15" s="24"/>
     </row>
     <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="32"/>
+      <c r="C16" s="24"/>
     </row>
     <row r="17" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="69" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="32"/>
+      <c r="C17" s="24"/>
     </row>
     <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="C18" s="32"/>
+      <c r="C18" s="24"/>
     </row>
     <row r="19" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="14" t="s">
         <v>155</v>
       </c>
       <c r="B19" s="3"/>
@@ -2348,134 +6917,134 @@
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A20" s="18">
+      <c r="A20" s="72">
         <v>2.1</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="32"/>
+      <c r="C20" s="24"/>
     </row>
     <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="18">
+      <c r="A21" s="74">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="32"/>
+      <c r="C21" s="24"/>
     </row>
     <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="18">
+      <c r="A22" s="76">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="32"/>
+      <c r="C22" s="24"/>
     </row>
     <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="18">
+      <c r="A23" s="78">
         <v>2.4</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="32"/>
+      <c r="C23" s="24"/>
     </row>
     <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="18">
+      <c r="A24" s="80">
         <v>2.5</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="32"/>
+      <c r="C24" s="24"/>
     </row>
     <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="18">
+      <c r="A25" s="82">
         <v>2.6</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="32"/>
+      <c r="C25" s="24"/>
     </row>
     <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="18">
+      <c r="A26" s="84">
         <v>2.7</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="32"/>
+      <c r="C26" s="24"/>
     </row>
     <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
+      <c r="A27" s="86">
         <v>2.8</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
     </row>
     <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="18">
+      <c r="A28" s="88">
         <v>2.9</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="89" t="s">
         <v>145</v>
       </c>
-      <c r="C28" s="32"/>
+      <c r="C28" s="24"/>
     </row>
     <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="32"/>
+      <c r="C29" s="24"/>
     </row>
     <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="18">
+      <c r="A30" s="92">
         <v>2.11</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="32"/>
+      <c r="C30" s="24"/>
     </row>
     <row r="31" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A31" s="18">
+      <c r="A31" s="94">
         <v>2.12</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="C31" s="32"/>
+      <c r="C31" s="24"/>
     </row>
     <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="18">
+      <c r="A32" s="96">
         <v>2.13</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="97" t="s">
         <v>157</v>
       </c>
-      <c r="C32" s="32"/>
+      <c r="C32" s="24"/>
     </row>
     <row r="33" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A33" s="18">
+      <c r="A33" s="98">
         <v>2.14</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="32"/>
+      <c r="C33" s="24"/>
     </row>
     <row r="34" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="14" t="s">
         <v>76</v>
       </c>
       <c r="B34" s="3"/>
@@ -2483,22 +7052,22 @@
       <c r="D34" s="3"/>
     </row>
     <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="32"/>
+      <c r="C35" s="24"/>
     </row>
     <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="32"/>
+      <c r="C36" s="24"/>
     </row>
     <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
@@ -2507,19 +7076,19 @@
       <c r="B37" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="32"/>
+      <c r="C37" s="24"/>
     </row>
     <row r="38" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="105" t="s">
         <v>158</v>
       </c>
-      <c r="C38" s="32"/>
+      <c r="C38" s="24"/>
     </row>
     <row r="39" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="14" t="s">
         <v>159</v>
       </c>
       <c r="B39" s="3"/>
@@ -2527,70 +7096,70 @@
       <c r="D39" s="3"/>
     </row>
     <row r="40" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="107" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="32"/>
+      <c r="C40" s="24"/>
     </row>
     <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="108" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="109" t="s">
         <v>161</v>
       </c>
-      <c r="C41" s="32"/>
+      <c r="C41" s="24"/>
     </row>
     <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="111" t="s">
         <v>162</v>
       </c>
-      <c r="C42" s="32"/>
+      <c r="C42" s="24"/>
     </row>
     <row r="43" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="113" t="s">
         <v>81</v>
       </c>
-      <c r="C43" s="32"/>
+      <c r="C43" s="24"/>
     </row>
     <row r="44" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="115" t="s">
         <v>163</v>
       </c>
-      <c r="C44" s="32"/>
+      <c r="C44" s="24"/>
     </row>
     <row r="45" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="117" t="s">
         <v>164</v>
       </c>
-      <c r="C45" s="32"/>
+      <c r="C45" s="24"/>
     </row>
     <row r="46" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="C46" s="32"/>
+      <c r="C46" s="24"/>
     </row>
     <row r="47" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="14" t="s">
         <v>85</v>
       </c>
       <c r="B47" s="3"/>
@@ -2598,66 +7167,66 @@
       <c r="D47" s="3"/>
     </row>
     <row r="48" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="C48" s="32"/>
+      <c r="C48" s="24"/>
     </row>
     <row r="49" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
     </row>
     <row r="50" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="124" t="s">
         <v>29</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="125" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
     </row>
     <row r="51" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="127" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
     </row>
     <row r="52" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
     </row>
     <row r="53" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="130" t="s">
         <v>110</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="131" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
     </row>
     <row r="54" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="14" t="s">
         <v>93</v>
       </c>
       <c r="B54" s="3"/>
@@ -2665,140 +7234,140 @@
       <c r="D54" s="3"/>
     </row>
     <row r="55" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="133" t="s">
         <v>91</v>
       </c>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
     </row>
     <row r="56" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="135" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
     </row>
     <row r="57" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="137" t="s">
         <v>143</v>
       </c>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
     </row>
     <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="138" t="s">
         <v>35</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="139" t="s">
         <v>94</v>
       </c>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
     </row>
     <row r="59" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="140" t="s">
         <v>36</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="141" t="s">
         <v>95</v>
       </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
     </row>
     <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="142" t="s">
         <v>49</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="143" t="s">
         <v>96</v>
       </c>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
     </row>
     <row r="61" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="144" t="s">
         <v>111</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="145" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
     </row>
     <row r="62" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="146" t="s">
         <v>112</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="147" t="s">
         <v>166</v>
       </c>
-      <c r="C62" s="32"/>
+      <c r="C62" s="24"/>
     </row>
     <row r="63" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="148" t="s">
         <v>113</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="149" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="32"/>
+      <c r="C63" s="24"/>
     </row>
     <row r="64" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="151" t="s">
         <v>97</v>
       </c>
-      <c r="C64" s="32"/>
+      <c r="C64" s="24"/>
     </row>
     <row r="65" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="153" t="s">
         <v>98</v>
       </c>
-      <c r="C65" s="32"/>
+      <c r="C65" s="24"/>
     </row>
     <row r="66" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="154" t="s">
         <v>116</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="155" t="s">
         <v>99</v>
       </c>
-      <c r="C66" s="32"/>
+      <c r="C66" s="24"/>
     </row>
     <row r="67" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="157" t="s">
         <v>100</v>
       </c>
-      <c r="C67" s="32"/>
+      <c r="C67" s="24"/>
     </row>
     <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="158" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="159" t="s">
         <v>125</v>
       </c>
-      <c r="C68" s="32"/>
+      <c r="C68" s="24"/>
     </row>
     <row r="69" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="14" t="s">
         <v>106</v>
       </c>
       <c r="B69" s="3"/>
@@ -2806,54 +7375,54 @@
       <c r="D69" s="3"/>
     </row>
     <row r="70" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="161" t="s">
         <v>105</v>
       </c>
-      <c r="C70" s="32"/>
+      <c r="C70" s="24"/>
     </row>
     <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="162" t="s">
         <v>38</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="163" t="s">
         <v>101</v>
       </c>
-      <c r="C71" s="32"/>
+      <c r="C71" s="24"/>
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="164" t="s">
         <v>39</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="165" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="32"/>
-      <c r="D72" s="32"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="167" t="s">
         <v>103</v>
       </c>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="168" t="s">
         <v>41</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="169" t="s">
         <v>104</v>
       </c>
-      <c r="C74" s="32"/>
+      <c r="C74" s="24"/>
     </row>
     <row r="75" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="14" t="s">
         <v>107</v>
       </c>
       <c r="B75" s="3"/>
@@ -2861,47 +7430,47 @@
       <c r="D75" s="3"/>
     </row>
     <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="170" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="171" t="s">
         <v>108</v>
       </c>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
     </row>
     <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="172" t="s">
         <v>119</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="173" t="s">
         <v>146</v>
       </c>
-      <c r="C77" s="32"/>
-      <c r="D77" s="33"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="25"/>
     </row>
     <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="174" t="s">
         <v>120</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="175" t="s">
         <v>147</v>
       </c>
-      <c r="C78" s="32"/>
-      <c r="D78" s="33"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="25"/>
     </row>
     <row r="79" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="176" t="s">
         <v>121</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="177" t="s">
         <v>167</v>
       </c>
-      <c r="C79" s="32"/>
-      <c r="D79" s="33"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="25"/>
     </row>
     <row r="80" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="17" t="s">
+      <c r="A80" s="14" t="s">
         <v>168</v>
       </c>
       <c r="B80" s="3"/>
@@ -2909,40 +7478,40 @@
       <c r="D80" s="3"/>
     </row>
     <row r="81" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="178" t="s">
         <v>122</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="179" t="s">
         <v>128</v>
       </c>
-      <c r="C81" s="32"/>
+      <c r="C81" s="24"/>
     </row>
     <row r="82" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="180" t="s">
         <v>126</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="181" t="s">
         <v>148</v>
       </c>
-      <c r="C82" s="32"/>
+      <c r="C82" s="24"/>
     </row>
     <row r="83" spans="1:3" ht="80" x14ac:dyDescent="0.2">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="182" t="s">
         <v>149</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="183" t="s">
         <v>150</v>
       </c>
-      <c r="C83" s="32"/>
+      <c r="C83" s="24"/>
     </row>
     <row r="84" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="184" t="s">
         <v>140</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="185" t="s">
         <v>127</v>
       </c>
-      <c r="C84" s="32"/>
+      <c r="C84" s="24"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B85" s="8"/>
@@ -3041,18 +7610,17 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="1.0629921259842521" bottom="1.0629921259842521" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="85" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;L&amp;G&amp;C&amp;18
 פרוטוקול בדיקה תקופתית - מתקן פוטו-וולטאי
 </oddHeader>
     <oddFooter>&amp;C&amp;G&amp;R&amp;P</oddFooter>
   </headerFooter>
-  <rowBreaks count="4" manualBreakCount="4">
-    <brk id="33" max="3" man="1"/>
-    <brk id="53" max="3" man="1"/>
-    <brk id="74" max="3" man="1"/>
-    <brk id="84" max="3" man="1"/>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="18" max="16383" man="1"/>
+    <brk id="46" max="16383" man="1"/>
+    <brk id="68" max="16383" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
   <tableParts count="1">
@@ -3067,232 +7635,231 @@
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1640625" style="1" customWidth="1"/>
-    <col min="3" max="8" width="12" style="1" customWidth="1"/>
+    <col min="1" max="3" width="10" style="1" customWidth="1"/>
+    <col min="4" max="8" width="14" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="33" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-    </row>
-    <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-    </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-    </row>
-    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-    </row>
-    <row r="6" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="34"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-    </row>
-    <row r="7" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="34"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-    </row>
-    <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-    </row>
-    <row r="9" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="34"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-    </row>
-    <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-    </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="34"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-    </row>
-    <row r="12" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-    </row>
-    <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-    </row>
-    <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="34"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-    </row>
-    <row r="15" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="34"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-    </row>
-    <row r="16" spans="1:8" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="36"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-    </row>
-    <row r="17" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="34"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-    </row>
-    <row r="18" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="34"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-    </row>
-    <row r="19" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="34"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-    </row>
-    <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="34"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="186"/>
+      <c r="B2" s="187"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="193"/>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="199"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="201"/>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="202"/>
+      <c r="B4" s="203"/>
+      <c r="C4" s="204"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="209"/>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
+      <c r="E5" s="214"/>
+      <c r="F5" s="215"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="217"/>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="218"/>
+      <c r="B6" s="219"/>
+      <c r="C6" s="220"/>
+      <c r="D6" s="221"/>
+      <c r="E6" s="222"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="224"/>
+      <c r="H6" s="225"/>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="226"/>
+      <c r="B7" s="227"/>
+      <c r="C7" s="228"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="230"/>
+      <c r="F7" s="231"/>
+      <c r="G7" s="232"/>
+      <c r="H7" s="233"/>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="234"/>
+      <c r="B8" s="235"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="238"/>
+      <c r="F8" s="239"/>
+      <c r="G8" s="240"/>
+      <c r="H8" s="241"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="242"/>
+      <c r="B9" s="243"/>
+      <c r="C9" s="244"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="247"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="249"/>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="250"/>
+      <c r="B10" s="251"/>
+      <c r="C10" s="252"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="255"/>
+      <c r="G10" s="256"/>
+      <c r="H10" s="257"/>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="258"/>
+      <c r="B11" s="259"/>
+      <c r="C11" s="260"/>
+      <c r="D11" s="261"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="263"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="265"/>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="266"/>
+      <c r="B12" s="267"/>
+      <c r="C12" s="268"/>
+      <c r="D12" s="269"/>
+      <c r="E12" s="270"/>
+      <c r="F12" s="271"/>
+      <c r="G12" s="272"/>
+      <c r="H12" s="273"/>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="274"/>
+      <c r="B13" s="275"/>
+      <c r="C13" s="276"/>
+      <c r="D13" s="277"/>
+      <c r="E13" s="278"/>
+      <c r="F13" s="279"/>
+      <c r="G13" s="280"/>
+      <c r="H13" s="281"/>
+    </row>
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="282"/>
+      <c r="B14" s="283"/>
+      <c r="C14" s="284"/>
+      <c r="D14" s="285"/>
+      <c r="E14" s="286"/>
+      <c r="F14" s="287"/>
+      <c r="G14" s="288"/>
+      <c r="H14" s="289"/>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="290"/>
+      <c r="B15" s="291"/>
+      <c r="C15" s="292"/>
+      <c r="D15" s="293"/>
+      <c r="E15" s="294"/>
+      <c r="F15" s="295"/>
+      <c r="G15" s="296"/>
+      <c r="H15" s="297"/>
+    </row>
+    <row r="16" spans="1:8" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="298"/>
+      <c r="B16" s="299"/>
+      <c r="C16" s="300"/>
+      <c r="D16" s="301"/>
+      <c r="E16" s="302"/>
+      <c r="F16" s="303"/>
+      <c r="G16" s="304"/>
+      <c r="H16" s="305"/>
+    </row>
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="306"/>
+      <c r="B17" s="307"/>
+      <c r="C17" s="308"/>
+      <c r="D17" s="309"/>
+      <c r="E17" s="310"/>
+      <c r="F17" s="311"/>
+      <c r="G17" s="312"/>
+      <c r="H17" s="313"/>
+    </row>
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="314"/>
+      <c r="B18" s="315"/>
+      <c r="C18" s="316"/>
+      <c r="D18" s="317"/>
+      <c r="E18" s="318"/>
+      <c r="F18" s="319"/>
+      <c r="G18" s="320"/>
+      <c r="H18" s="321"/>
+    </row>
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="322"/>
+      <c r="B19" s="323"/>
+      <c r="C19" s="324"/>
+      <c r="D19" s="325"/>
+      <c r="E19" s="326"/>
+      <c r="F19" s="327"/>
+      <c r="G19" s="328"/>
+      <c r="H19" s="329"/>
+    </row>
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="330"/>
+      <c r="B20" s="331"/>
+      <c r="C20" s="332"/>
+      <c r="D20" s="333"/>
+      <c r="E20" s="334"/>
+      <c r="F20" s="335"/>
+      <c r="G20" s="336"/>
+      <c r="H20" s="337"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="1.0629921259842521" bottom="1.0629921259842521" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;L&amp;G&amp;C&amp;18
 טופס בדיקות חשמליות - DC 
@@ -3318,11 +7885,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4A5D52B-3746-4E43-9695-1C505ED38B54}">
   <sheetPr codeName="גיליון5"/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.1640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" style="13" customWidth="1"/>
     <col min="3" max="3" width="21" style="7" customWidth="1"/>
     <col min="4" max="4" width="34.33203125" style="7" customWidth="1"/>
     <col min="5" max="16384" width="8.83203125" style="7"/>
@@ -3338,335 +7905,415 @@
       <c r="C1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>137</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="25"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="19"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="19"/>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="16" t="s">
         <v>138</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="25"/>
+      <c r="D7" s="18"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="17" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="19"/>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="17" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="19"/>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="17" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="16" t="s">
         <v>139</v>
       </c>
       <c r="B12" s="10"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="18"/>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="24">
+      <c r="A13" s="17">
         <v>3.1</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="19"/>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24">
+      <c r="A14" s="17">
         <v>3.2</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="19"/>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24">
+      <c r="A15" s="17">
         <v>3.3</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="19"/>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="24">
+      <c r="A16" s="17">
         <v>3.4</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="19"/>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="24">
+      <c r="A17" s="17">
         <v>3.5</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="19"/>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="24">
+      <c r="A18" s="17">
         <v>3.6</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="19"/>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="16" t="s">
         <v>174</v>
       </c>
       <c r="B19" s="10"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="20"/>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="24">
+      <c r="A20" s="17">
         <v>4.0999999999999996</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="19"/>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="24">
+      <c r="A21" s="17">
         <v>4.2</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="19"/>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="24">
+      <c r="A22" s="17">
         <v>4.3</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="19"/>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="24">
+      <c r="A23" s="17">
         <v>4.4000000000000004</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="19"/>
     </row>
     <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="24">
+      <c r="A24" s="17">
         <v>4.5</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="19"/>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24">
+      <c r="A25" s="17">
         <v>4.5999999999999996</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="19"/>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="16" t="s">
         <v>175</v>
       </c>
       <c r="B26" s="10"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="20"/>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="24">
+      <c r="A27" s="17">
         <v>5.0999999999999996</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="19"/>
     </row>
     <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="24">
+      <c r="A28" s="17">
         <v>5.2</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="19"/>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="24">
+      <c r="A29" s="17">
         <v>5.3</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="38"/>
-      <c r="D29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="19"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="24">
+      <c r="A30" s="17">
         <v>5.4</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="38"/>
-      <c r="D30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="19"/>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="24">
+      <c r="A31" s="17">
         <v>5.5</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="38"/>
-      <c r="D31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="19"/>
     </row>
     <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="24">
+      <c r="A32" s="17">
         <v>5.6</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="19"/>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="16" t="s">
         <v>176</v>
       </c>
       <c r="B33" s="10"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="20"/>
     </row>
     <row r="34" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="20" t="s">
+      <c r="A34" s="17">
+        <v>6.1</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="41"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="19"/>
+    </row>
+    <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="17">
+        <v>6.2</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="26"/>
+      <c r="D35" s="19"/>
+    </row>
+    <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="17">
+        <v>6.3</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="26"/>
+      <c r="D36" s="19"/>
+    </row>
+    <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="17">
+        <v>6.4</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="19"/>
+    </row>
+    <row r="38" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C38" s="26"/>
+      <c r="D38" s="19"/>
+    </row>
+    <row r="39" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="17">
+        <v>6.6</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="26"/>
+      <c r="D39" s="19"/>
+    </row>
+    <row r="40" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="17">
+        <v>6.7</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" s="26"/>
+      <c r="D40" s="19"/>
+    </row>
+    <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="17">
+        <v>6.8</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" s="26"/>
+      <c r="D41" s="19"/>
+    </row>
+    <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="17">
+        <v>6.9</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="26"/>
+      <c r="D42" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="1.0629921259842521" bottom="1.0629921259842521" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;L&amp;G&amp;C&amp;18טופס בדיקות חשמליות- AC כיוונון הגנות
 </oddHeader>
@@ -3685,81 +8332,82 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="32.1640625" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="37" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="22"/>
-    </row>
-    <row r="3" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="22"/>
-    </row>
-    <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="22"/>
-    </row>
-    <row r="5" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="22"/>
-    </row>
-    <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="22"/>
-    </row>
-    <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="22"/>
-    </row>
-    <row r="8" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="22"/>
-    </row>
-    <row r="9" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="22"/>
-    </row>
-    <row r="10" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="42"/>
+    <row r="2" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="40"/>
+    </row>
+    <row r="3" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+    </row>
+    <row r="4" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="40"/>
+    </row>
+    <row r="5" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="38"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="40"/>
+    </row>
+    <row r="6" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="38"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="40"/>
+    </row>
+    <row r="7" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="38"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40"/>
+    </row>
+    <row r="8" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="38"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="40"/>
+    </row>
+    <row r="9" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
+    </row>
+    <row r="10" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="41"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
-      <c r="D10" s="22"/>
+      <c r="D10" s="43"/>
     </row>
   </sheetData>
-  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="1.0629921259842521" bottom="1.0629921259842521" header="0" footer="0"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="1.35" bottom="1.0629921259842521" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G&amp;C&amp;18
